--- a/ميكانيكا ترم ثاني.xlsx
+++ b/ميكانيكا ترم ثاني.xlsx
@@ -442,19 +442,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J2">
         <v>48</v>
       </c>
       <c r="K2">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -474,19 +474,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>4</v>
       </c>
       <c r="H3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J3">
         <v>44</v>
       </c>
       <c r="K3">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4">
@@ -826,19 +826,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>7</v>
       </c>
       <c r="H14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J14">
         <v>15</v>
       </c>
       <c r="K14">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -1082,19 +1082,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G22">
         <v>7</v>
       </c>
       <c r="H22">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J22">
         <v>56</v>
       </c>
       <c r="K22">
-        <v>66</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23">
@@ -1114,19 +1114,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>9</v>
       </c>
       <c r="H23">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J23">
         <v>33</v>
       </c>
       <c r="K23">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="24">
@@ -1210,19 +1210,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J26">
         <v>23</v>
       </c>
       <c r="K26">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -1338,19 +1338,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G30">
         <v>8</v>
       </c>
       <c r="H30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J30">
         <v>36</v>
       </c>
       <c r="K30">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
@@ -1646,19 +1646,19 @@
         <v>مستجد</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8">
         <v>11</v>
       </c>
       <c r="H8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8">
         <v>61</v>
       </c>
       <c r="K8">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -2062,19 +2062,19 @@
         <v>مستجد</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J21">
         <v>4</v>
       </c>
       <c r="K21">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -2158,19 +2158,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>10</v>
       </c>
       <c r="H24">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24">
         <v>52</v>
       </c>
       <c r="K24">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -2562,19 +2562,19 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>8</v>
       </c>
       <c r="H5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J5">
         <v>18</v>
       </c>
       <c r="K5">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -2626,19 +2626,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>8</v>
       </c>
       <c r="H7">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J7">
         <v>53</v>
       </c>
       <c r="K7">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -2690,19 +2690,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>5</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J9">
         <v>5</v>
       </c>
       <c r="K9">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -2754,19 +2754,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>13</v>
       </c>
       <c r="H11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J11">
         <v>62</v>
       </c>
       <c r="K11">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -2786,19 +2786,19 @@
         <v>مستجد</v>
       </c>
       <c r="F12">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G12">
         <v>6</v>
       </c>
       <c r="H12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J12">
         <v>36</v>
       </c>
       <c r="K12">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13">
@@ -3234,19 +3234,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>4</v>
       </c>
       <c r="H26">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26">
         <v>31</v>
       </c>
       <c r="K26">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -3394,19 +3394,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G31">
         <v>8</v>
       </c>
       <c r="H31">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J31">
         <v>29</v>
       </c>
       <c r="K31">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -3510,19 +3510,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J3">
         <v>37</v>
       </c>
       <c r="K3">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -3574,19 +3574,19 @@
         <v>مستجد</v>
       </c>
       <c r="F5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G5">
         <v>6</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J5">
         <v>48</v>
       </c>
       <c r="K5">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
@@ -3734,19 +3734,19 @@
         <v>مستجد</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <v>2</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J10">
         <v>49</v>
       </c>
       <c r="K10">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -3926,19 +3926,19 @@
         <v>مستجد</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J16">
         <v>22</v>
       </c>
       <c r="K16">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17">
@@ -4054,19 +4054,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>6</v>
       </c>
       <c r="H20">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J20">
         <v>27</v>
       </c>
       <c r="K20">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -4150,19 +4150,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G23" t="str">
         <v>غ</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J23">
         <v>32</v>
       </c>
       <c r="K23">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="24">
@@ -4182,19 +4182,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="H24">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J24">
         <v>6</v>
       </c>
       <c r="K24">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -4214,19 +4214,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G25">
         <v>5</v>
       </c>
       <c r="H25">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J25">
         <v>31</v>
       </c>
       <c r="K25">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
@@ -4246,19 +4246,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>6</v>
       </c>
       <c r="H26">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26">
         <v>23</v>
       </c>
       <c r="K26">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -4278,19 +4278,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G27">
         <v>6</v>
       </c>
       <c r="H27">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J27">
         <v>9</v>
       </c>
       <c r="K27">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -4342,19 +4342,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J29">
         <v>19</v>
       </c>
       <c r="K29">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -4406,19 +4406,19 @@
         <v>مستجد</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G31">
         <v>5</v>
       </c>
       <c r="H31">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J31">
         <v>30</v>
       </c>
       <c r="K31">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -4490,19 +4490,19 @@
         <v>مستجد</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2">
         <v>11</v>
       </c>
       <c r="H2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J2">
         <v>57</v>
       </c>
       <c r="K2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
@@ -4522,19 +4522,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>30</v>
       </c>
       <c r="K3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4">
@@ -4618,19 +4618,19 @@
         <v>مستجد</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>3</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J6">
         <v>23</v>
       </c>
       <c r="K6">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -4778,19 +4778,19 @@
         <v>مستجد</v>
       </c>
       <c r="F11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>6</v>
       </c>
       <c r="H11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11">
         <v>37</v>
       </c>
       <c r="K11">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -5002,19 +5002,19 @@
         <v>مستجد</v>
       </c>
       <c r="F18">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18">
         <v>7</v>
       </c>
       <c r="H18">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J18">
         <v>14</v>
       </c>
       <c r="K18">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -5034,19 +5034,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J19">
         <v>8</v>
       </c>
       <c r="K19">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -5130,19 +5130,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>3</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J22">
         <v>39</v>
       </c>
       <c r="K22">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
@@ -5194,19 +5194,19 @@
         <v>مستجد</v>
       </c>
       <c r="F24">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>11</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J24">
         <v>58</v>
       </c>
       <c r="K24">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
@@ -5226,19 +5226,19 @@
         <v>مستجد</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G25">
         <v>10</v>
       </c>
       <c r="H25">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J25">
         <v>35</v>
       </c>
       <c r="K25">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26">
@@ -5322,19 +5322,19 @@
         <v>مستجد</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G28">
         <v>10</v>
       </c>
       <c r="H28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J28">
         <v>46</v>
       </c>
       <c r="K28">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
@@ -5354,19 +5354,19 @@
         <v>مستجد</v>
       </c>
       <c r="F29">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G29">
         <v>6</v>
       </c>
       <c r="H29">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J29">
         <v>16</v>
       </c>
       <c r="K29">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30">
@@ -5386,19 +5386,19 @@
         <v>مستجد</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G30">
         <v>3</v>
       </c>
       <c r="H30">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="J30">
         <v>4</v>
       </c>
       <c r="K30">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
@@ -5534,19 +5534,19 @@
         <v>مستجد</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>3</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J3">
         <v>5</v>
       </c>
       <c r="K3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -5662,19 +5662,19 @@
         <v>مستجد</v>
       </c>
       <c r="F7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7">
         <v>6</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7">
         <v>19</v>
       </c>
       <c r="K7">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -5854,19 +5854,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G13">
         <v>8</v>
       </c>
       <c r="H13">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J13">
         <v>42</v>
       </c>
       <c r="K13">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -5886,19 +5886,19 @@
         <v>مستجد</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G14">
         <v>9</v>
       </c>
       <c r="H14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J14">
         <v>28</v>
       </c>
       <c r="K14">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -6046,19 +6046,19 @@
         <v>مستجد</v>
       </c>
       <c r="F19">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G19">
         <v>3</v>
       </c>
       <c r="H19">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J19">
         <v>4</v>
       </c>
       <c r="K19">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6142,19 +6142,19 @@
         <v>مستجد</v>
       </c>
       <c r="F22">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>15</v>
       </c>
       <c r="H22">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J22">
         <v>63</v>
       </c>
       <c r="K22">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
@@ -6174,19 +6174,19 @@
         <v>مستجد</v>
       </c>
       <c r="F23">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23">
         <v>16</v>
       </c>
       <c r="K23">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24">
@@ -6270,19 +6270,19 @@
         <v>مستجد</v>
       </c>
       <c r="F26">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G26">
         <v>11</v>
       </c>
       <c r="H26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J26">
         <v>50</v>
       </c>
       <c r="K26">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27">
@@ -6302,19 +6302,19 @@
         <v>مستجد</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G27" t="str">
         <v>غ</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J27">
         <v>11</v>
       </c>
       <c r="K27">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -6738,19 +6738,19 @@
         <v>مستجد</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9">
         <v>10</v>
       </c>
       <c r="H9">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J9">
         <v>49</v>
       </c>
       <c r="K9">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
@@ -6866,19 +6866,19 @@
         <v>مستجد</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J13">
         <v>4</v>
       </c>
       <c r="K13">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -6994,19 +6994,19 @@
         <v>مستجد</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>9</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J17">
         <v>38</v>
       </c>
       <c r="K17">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -7090,19 +7090,19 @@
         <v>مستجد</v>
       </c>
       <c r="F20">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G20">
         <v>8</v>
       </c>
       <c r="H20">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20">
         <v>42</v>
       </c>
       <c r="K20">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -7198,7 +7198,7 @@
         <v>4</v>
       </c>
       <c r="K23">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24">
@@ -7218,19 +7218,19 @@
         <v>باقي</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24">
         <v>6</v>
       </c>
       <c r="H24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J24">
         <v>26</v>
       </c>
       <c r="K24">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25">
@@ -7297,7 +7297,7 @@
         <v>55</v>
       </c>
       <c r="K26">
-        <v>76</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27">
@@ -7349,19 +7349,19 @@
         <v>باقي</v>
       </c>
       <c r="F28">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G28" t="str">
         <v>غ</v>
       </c>
       <c r="H28">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J28">
         <v>23</v>
       </c>
       <c r="K28">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29">
@@ -7381,19 +7381,19 @@
         <v>باقي</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J29">
         <v>6</v>
       </c>
       <c r="K29">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30">
@@ -7460,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -7564,19 +7564,19 @@
         <v>باقي</v>
       </c>
       <c r="F3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J3">
         <v>14</v>
       </c>
       <c r="K3">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -7608,7 +7608,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>10</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -7675,7 +7675,7 @@
         <v>1</v>
       </c>
       <c r="K6">
-        <v>4</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
@@ -7707,7 +7707,7 @@
         <v>11</v>
       </c>
       <c r="K7">
-        <v>11</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
@@ -7739,7 +7739,7 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -7803,7 +7803,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -7835,7 +7835,7 @@
         <v>22</v>
       </c>
       <c r="K11">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
@@ -7983,19 +7983,19 @@
         <v>باقي</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
       </c>
       <c r="H16">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J16">
         <v>9</v>
       </c>
       <c r="K16">
-        <v>14</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -8059,7 +8059,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19">
@@ -8155,7 +8155,7 @@
         <v>25</v>
       </c>
       <c r="K21">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -8175,19 +8175,19 @@
         <v>مستجد بفرصة</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G22">
         <v>3</v>
       </c>
       <c r="H22">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="J22">
         <v>29</v>
       </c>
       <c r="K22">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
